--- a/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado</t>
+          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,64</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,57</t>
+          <t>7,39; 8,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,62</t>
+          <t>7,68; 8,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,6</t>
+          <t>6,85; 7,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,21</t>
+          <t>7,46; 8,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,91</t>
+          <t>6,82; 7,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,19 +712,19 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,21</t>
+          <t>7,51; 8,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,03</t>
+          <t>7,38; 8,06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -734,47 +734,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,09</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,79</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,66</t>
         </is>
       </c>
     </row>
@@ -787,398 +787,65 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,39; 8,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,68; 8,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,85; 7,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,46; 8,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,82; 7,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,95; 7,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,51; 8,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,38; 8,06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,64</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 8,62</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 7,48</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,79; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,51</t>
+          <t>7,42; 8,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,6</t>
+          <t>7,68; 8,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,57</t>
+          <t>6,83; 7,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,23</t>
+          <t>7,38; 8,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,87</t>
+          <t>6,82; 7,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,48</t>
+          <t>6,91; 7,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,21</t>
+          <t>7,53; 8,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,06</t>
+          <t>7,34; 8,04</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,79; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,51</t>
+          <t>7,42; 8,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,6</t>
+          <t>7,68; 8,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,57</t>
+          <t>6,83; 7,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,23</t>
+          <t>7,38; 8,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,87</t>
+          <t>6,82; 7,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,48</t>
+          <t>6,91; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,21</t>
+          <t>7,53; 8,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,06</t>
+          <t>7,34; 8,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,65</t>
+          <t>6,85; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,57</t>
+          <t>7,42; 8,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,59</t>
+          <t>6,85; 7,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,59</t>
+          <t>6,8; 7,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,17</t>
+          <t>7,37; 8,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,88</t>
+          <t>7,69; 8,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,47</t>
+          <t>6,95; 7,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,22</t>
+          <t>7,52; 8,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,04</t>
+          <t>7,37; 8,03</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,65</t>
+          <t>6,85; 7,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,57</t>
+          <t>7,42; 8,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,59</t>
+          <t>6,85; 7,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,59</t>
+          <t>6,8; 7,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,17</t>
+          <t>7,37; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,88</t>
+          <t>7,69; 8,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,47</t>
+          <t>6,95; 7,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,22</t>
+          <t>7,52; 8,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,04</t>
+          <t>7,37; 8,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,229 +627,117 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.194568821393071</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.78669216585527</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.241462922260872</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.201851859521645</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7.793434878057755</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8.090397653694831</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>7.197960668262682</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>7.789996458275741</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.664646716399024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,6</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,64</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,57</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 8,62</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 7,48</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.84520413204228</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.421563673088825</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.853564913398673</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>6.797748991603733</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7.373357305316943</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>7.690486094829057</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>6.950997366244207</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.522212523575002</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7.366378571170508</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.598708818335283</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.209710042480397</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.907356058578277</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.639725248553726</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8.571050751942703</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.616580532381422</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>7.482981390075063</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>8.213203967999696</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.032875538653988</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 7,91</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,64</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 8,62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,95; 7,48</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 8,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A4:A6"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
